--- a/IaR_GaR_April_2026/Outputs/forecast_evaluation/comparison_fcst_eval_growth.xlsx
+++ b/IaR_GaR_April_2026/Outputs/forecast_evaluation/comparison_fcst_eval_growth.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -20,13 +20,14 @@
     <sheet name="MW_pval" sheetId="12" r:id="rId14"/>
     <sheet name="CRPS_mean" sheetId="13" r:id="rId15"/>
     <sheet name="wCRPS_left_mean" sheetId="14" r:id="rId16"/>
+    <sheet name="GMM_summary" sheetId="15" r:id="rId17"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="622" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="71">
   <si>
     <t>horizon</t>
   </si>
@@ -41,12 +42,210 @@
   </si>
   <si>
     <t>qr_fr</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>GMM_KS_std_bonf_w_wi_1</t>
+  </si>
+  <si>
+    <t>GMM_KS_std_bonf_w_wi_2</t>
+  </si>
+  <si>
+    <t>GMM_KS_std_bonf_w_wi_3</t>
+  </si>
+  <si>
+    <t>GMM_CVM_std_bonf_w_wi_1</t>
+  </si>
+  <si>
+    <t>GMM_CVM_std_bonf_w_wi_2</t>
+  </si>
+  <si>
+    <t>GMM_CVM_std_bonf_w_wi_3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -89,25 +288,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="12.453125" customWidth="true"/>
-    <col min="3" max="3" width="12.453125" customWidth="true"/>
-    <col min="4" max="4" width="12.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
     <col min="5" max="5" width="12.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -121,7 +320,7 @@
         <v>0.10007702852204303</v>
       </c>
       <c r="C2" s="0">
-        <v>0.20999610407924452</v>
+        <v>0.19042743907996229</v>
       </c>
       <c r="D2" s="0">
         <v>0.19528968220564347</v>
@@ -138,7 +337,7 @@
         <v>0.13313107438852911</v>
       </c>
       <c r="C3" s="0">
-        <v>0.16997723166227152</v>
+        <v>0.1504135714879189</v>
       </c>
       <c r="D3" s="0">
         <v>0.18277082151778923</v>
@@ -155,7 +354,7 @@
         <v>0.11283698338954662</v>
       </c>
       <c r="C4" s="0">
-        <v>0.27058345577563592</v>
+        <v>0.20169170657447</v>
       </c>
       <c r="D4" s="0">
         <v>0.24742932092734116</v>
@@ -172,7 +371,7 @@
         <v>0.12388222160712559</v>
       </c>
       <c r="C5" s="0">
-        <v>0.30769230769230771</v>
+        <v>0.22397972850475989</v>
       </c>
       <c r="D5" s="0">
         <v>0.26778041316153073</v>
@@ -189,7 +388,7 @@
         <v>0.15283323644495128</v>
       </c>
       <c r="C6" s="0">
-        <v>0.35562657325353819</v>
+        <v>0.28594408866230941</v>
       </c>
       <c r="D6" s="0">
         <v>0.28900685160468542</v>
@@ -206,7 +405,7 @@
         <v>0.15073700279685842</v>
       </c>
       <c r="C7" s="0">
-        <v>0.45721812986264321</v>
+        <v>0.35199484598127867</v>
       </c>
       <c r="D7" s="0">
         <v>0.36659949568749228</v>
@@ -223,7 +422,7 @@
         <v>0.16806600373788627</v>
       </c>
       <c r="C8" s="0">
-        <v>0.47283288234112042</v>
+        <v>0.32187935206638957</v>
       </c>
       <c r="D8" s="0">
         <v>0.40732985329200311</v>
@@ -240,7 +439,7 @@
         <v>0.23459311113940429</v>
       </c>
       <c r="C9" s="0">
-        <v>0.52308843077960943</v>
+        <v>0.36187354213386153</v>
       </c>
       <c r="D9" s="0">
         <v>0.39279924721648096</v>
@@ -257,7 +456,7 @@
         <v>0.24570923638360065</v>
       </c>
       <c r="C10" s="0">
-        <v>0.48916361578802026</v>
+        <v>0.2978827399962517</v>
       </c>
       <c r="D10" s="0">
         <v>0.33929752641304667</v>
@@ -274,7 +473,7 @@
         <v>0.29225860952819482</v>
       </c>
       <c r="C11" s="0">
-        <v>0.41656429107579801</v>
+        <v>0.26042813027814826</v>
       </c>
       <c r="D11" s="0">
         <v>0.27238711624176359</v>
@@ -291,7 +490,7 @@
         <v>0.33140867251728079</v>
       </c>
       <c r="C12" s="0">
-        <v>0.40395934043696907</v>
+        <v>0.25603354211073448</v>
       </c>
       <c r="D12" s="0">
         <v>0.22139964042730431</v>
@@ -308,7 +507,7 @@
         <v>0.39360645766025248</v>
       </c>
       <c r="C13" s="0">
-        <v>0.46881227558369992</v>
+        <v>0.19197662244303593</v>
       </c>
       <c r="D13" s="0">
         <v>0.18738247268664709</v>
@@ -325,7 +524,7 @@
         <v>0.35989221614525913</v>
       </c>
       <c r="C14" s="0">
-        <v>0.33175215381427048</v>
+        <v>0.21241242933645166</v>
       </c>
       <c r="D14" s="0">
         <v>0.23146430357573189</v>
@@ -343,25 +542,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="13.453125" customWidth="true"/>
-    <col min="3" max="3" width="13.453125" customWidth="true"/>
-    <col min="4" max="4" width="13.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -375,7 +574,7 @@
         <v>0.51511571868168426</v>
       </c>
       <c r="C2" s="0">
-        <v>0.072904990163292438</v>
+        <v>0.040861441346580096</v>
       </c>
       <c r="D2" s="0">
         <v>0.21311516804565189</v>
@@ -392,7 +591,7 @@
         <v>0.45604371677887579</v>
       </c>
       <c r="C3" s="0">
-        <v>0.27854450036685408</v>
+        <v>0.3499015278032358</v>
       </c>
       <c r="D3" s="0">
         <v>0.10137968663420716</v>
@@ -409,7 +608,7 @@
         <v>0.45997781705462315</v>
       </c>
       <c r="C4" s="0">
-        <v>0.072121371964353642</v>
+        <v>0.12812978817280407</v>
       </c>
       <c r="D4" s="0">
         <v>0.066553138230247111</v>
@@ -426,7 +625,7 @@
         <v>0.58573629906961866</v>
       </c>
       <c r="C5" s="0">
-        <v>0.089774499926810525</v>
+        <v>0.090306168490604466</v>
       </c>
       <c r="D5" s="0">
         <v>0.144187928461464</v>
@@ -443,7 +642,7 @@
         <v>0.75061705183536609</v>
       </c>
       <c r="C6" s="0">
-        <v>0.15029632173057339</v>
+        <v>0.1567451803233213</v>
       </c>
       <c r="D6" s="0">
         <v>0.173837641152077</v>
@@ -460,7 +659,7 @@
         <v>0.57165889209204424</v>
       </c>
       <c r="C7" s="0">
-        <v>0.1506748295540058</v>
+        <v>0.15642457466498805</v>
       </c>
       <c r="D7" s="0">
         <v>0.24757662359272214</v>
@@ -477,7 +676,7 @@
         <v>0.44368593953730973</v>
       </c>
       <c r="C8" s="0">
-        <v>0.15535503479096024</v>
+        <v>0.10946686573774889</v>
       </c>
       <c r="D8" s="0">
         <v>0.36640191956100954</v>
@@ -494,7 +693,7 @@
         <v>0.26860072607893337</v>
       </c>
       <c r="C9" s="0">
-        <v>0.15147094263469763</v>
+        <v>0.17082870123571225</v>
       </c>
       <c r="D9" s="0">
         <v>0.42036874274727265</v>
@@ -511,7 +710,7 @@
         <v>0.15093661027117178</v>
       </c>
       <c r="C10" s="0">
-        <v>0.25648932249187939</v>
+        <v>0.29624524980235356</v>
       </c>
       <c r="D10" s="0">
         <v>0.5103199303494883</v>
@@ -528,7 +727,7 @@
         <v>0.076148777832890646</v>
       </c>
       <c r="C11" s="0">
-        <v>0.4946785218387626</v>
+        <v>0.5260153193748236</v>
       </c>
       <c r="D11" s="0">
         <v>0.40795410531987608</v>
@@ -545,7 +744,7 @@
         <v>0.056549790673129263</v>
       </c>
       <c r="C12" s="0">
-        <v>0.59371770979567895</v>
+        <v>0.45313436626608816</v>
       </c>
       <c r="D12" s="0">
         <v>0.24276946426442847</v>
@@ -562,7 +761,7 @@
         <v>0.1018095738734518</v>
       </c>
       <c r="C13" s="0">
-        <v>0.29724435225783874</v>
+        <v>0.53008543088784188</v>
       </c>
       <c r="D13" s="0">
         <v>0.17437083556969757</v>
@@ -579,7 +778,7 @@
         <v>0.22131049463475894</v>
       </c>
       <c r="C14" s="0">
-        <v>0.31726730430275407</v>
+        <v>0.44578043386097388</v>
       </c>
       <c r="D14" s="0">
         <v>0.23396031947262286</v>
@@ -597,25 +796,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="11.453125" customWidth="true"/>
-    <col min="3" max="3" width="11.453125" customWidth="true"/>
-    <col min="4" max="4" width="11.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="11.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -629,7 +828,7 @@
         <v>4.1111583332061281</v>
       </c>
       <c r="C2" s="0">
-        <v>13.244713991578351</v>
+        <v>15.82192835928117</v>
       </c>
       <c r="D2" s="0">
         <v>4.0032542743264541</v>
@@ -646,7 +845,7 @@
         <v>6.107590822047519</v>
       </c>
       <c r="C3" s="0">
-        <v>5.8772243943090139</v>
+        <v>10.46746225873884</v>
       </c>
       <c r="D3" s="0">
         <v>6.9213533452461649</v>
@@ -663,7 +862,7 @@
         <v>6.9123438131681594</v>
       </c>
       <c r="C4" s="0">
-        <v>13.882954020606954</v>
+        <v>9.5495873928723984</v>
       </c>
       <c r="D4" s="0">
         <v>9.4342579176117898</v>
@@ -680,7 +879,7 @@
         <v>3.3533609613386486</v>
       </c>
       <c r="C5" s="0">
-        <v>9.7460625153601583</v>
+        <v>9.3414550872306528</v>
       </c>
       <c r="D5" s="0">
         <v>6.7972159573074356</v>
@@ -697,7 +896,7 @@
         <v>2.0158574168591179</v>
       </c>
       <c r="C6" s="0">
-        <v>7.1796671115186106</v>
+        <v>4.7194310605114298</v>
       </c>
       <c r="D6" s="0">
         <v>9.0585344351617341</v>
@@ -714,7 +913,7 @@
         <v>2.3080714870344909</v>
       </c>
       <c r="C7" s="0">
-        <v>8.6642550125571063</v>
+        <v>6.8412602823854787</v>
       </c>
       <c r="D7" s="0">
         <v>7.0538962357389439</v>
@@ -731,7 +930,7 @@
         <v>3.3631265129041314</v>
       </c>
       <c r="C8" s="0">
-        <v>8.8439374281388972</v>
+        <v>11.349975271077838</v>
       </c>
       <c r="D8" s="0">
         <v>10.084045641856228</v>
@@ -748,7 +947,7 @@
         <v>4.6237549118250092</v>
       </c>
       <c r="C9" s="0">
-        <v>8.9826812380829022</v>
+        <v>7.1469607856794353</v>
       </c>
       <c r="D9" s="0">
         <v>8.6037762696578586</v>
@@ -765,7 +964,7 @@
         <v>6.4472357503153956</v>
       </c>
       <c r="C10" s="0">
-        <v>6.253146963174939</v>
+        <v>6.3892371751934274</v>
       </c>
       <c r="D10" s="0">
         <v>6.5883295803771622</v>
@@ -782,7 +981,7 @@
         <v>8.6943311580295841</v>
       </c>
       <c r="C11" s="0">
-        <v>5.1922521416518466</v>
+        <v>5.4737174269237494</v>
       </c>
       <c r="D11" s="0">
         <v>4.6954331884756968</v>
@@ -799,7 +998,7 @@
         <v>12.632358894313612</v>
       </c>
       <c r="C12" s="0">
-        <v>3.7641875501081201</v>
+        <v>2.7599610028432462</v>
       </c>
       <c r="D12" s="0">
         <v>9.659520506900213</v>
@@ -816,7 +1015,7 @@
         <v>8.9502473630389936</v>
       </c>
       <c r="C13" s="0">
-        <v>7.3330871835989671</v>
+        <v>3.2404909078550901</v>
       </c>
       <c r="D13" s="0">
         <v>8.8031042631781737</v>
@@ -833,7 +1032,7 @@
         <v>7.9121407376808941</v>
       </c>
       <c r="C14" s="0">
-        <v>9.5654007072640681</v>
+        <v>4.2101798133626591</v>
       </c>
       <c r="D14" s="0">
         <v>8.6192913236775937</v>
@@ -851,25 +1050,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="13.453125" customWidth="true"/>
-    <col min="3" max="3" width="13.453125" customWidth="true"/>
-    <col min="4" max="4" width="13.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -883,7 +1082,7 @@
         <v>0.53352551842039031</v>
       </c>
       <c r="C2" s="0">
-        <v>0.021190333797302285</v>
+        <v>0.0073713006231521661</v>
       </c>
       <c r="D2" s="0">
         <v>0.54894750960427818</v>
@@ -900,7 +1099,7 @@
         <v>0.29589022403405973</v>
       </c>
       <c r="C3" s="0">
-        <v>0.31834945986092889</v>
+        <v>0.063022960106911774</v>
       </c>
       <c r="D3" s="0">
         <v>0.22655538104628326</v>
@@ -917,7 +1116,7 @@
         <v>0.22724146764479314</v>
       </c>
       <c r="C4" s="0">
-        <v>0.016370252852729306</v>
+        <v>0.089050991537168112</v>
       </c>
       <c r="D4" s="0">
         <v>0.092947178029276656</v>
@@ -934,7 +1133,7 @@
         <v>0.64568257323324696</v>
       </c>
       <c r="C5" s="0">
-        <v>0.082758631232249691</v>
+        <v>0.096195566385820719</v>
       </c>
       <c r="D5" s="0">
         <v>0.23616371508040046</v>
@@ -951,7 +1150,7 @@
         <v>0.84694653799008512</v>
       </c>
       <c r="C6" s="0">
-        <v>0.20761749450406652</v>
+        <v>0.45107125756402067</v>
       </c>
       <c r="D6" s="0">
         <v>0.10675207022273914</v>
@@ -968,7 +1167,7 @@
         <v>0.80508066182165328</v>
       </c>
       <c r="C7" s="0">
-        <v>0.12322885535584471</v>
+        <v>0.23271620589900577</v>
       </c>
       <c r="D7" s="0">
         <v>0.21666273924739599</v>
@@ -985,7 +1184,7 @@
         <v>0.64419177001244354</v>
       </c>
       <c r="C8" s="0">
-        <v>0.11545323255412565</v>
+        <v>0.044865966985496941</v>
       </c>
       <c r="D8" s="0">
         <v>0.072888575834855418</v>
@@ -1002,7 +1201,7 @@
         <v>0.46349808824833905</v>
       </c>
       <c r="C9" s="0">
-        <v>0.1097569422265483</v>
+        <v>0.20993808632549316</v>
       </c>
       <c r="D9" s="0">
         <v>0.12595070325310753</v>
@@ -1019,7 +1218,7 @@
         <v>0.26509915508859194</v>
       </c>
       <c r="C10" s="0">
-        <v>0.28236011767628333</v>
+        <v>0.27016473843792077</v>
       </c>
       <c r="D10" s="0">
         <v>0.25310024952240395</v>
@@ -1036,7 +1235,7 @@
         <v>0.1218951668809175</v>
       </c>
       <c r="C11" s="0">
-        <v>0.39287105825216462</v>
+        <v>0.36083646851955975</v>
       </c>
       <c r="D11" s="0">
         <v>0.45416818752724286</v>
@@ -1053,7 +1252,7 @@
         <v>0.027078659840095942</v>
       </c>
       <c r="C12" s="0">
-        <v>0.58384154350346362</v>
+        <v>0.73693349696535093</v>
       </c>
       <c r="D12" s="0">
         <v>0.085477826738126317</v>
@@ -1070,7 +1269,7 @@
         <v>0.11106515460428112</v>
       </c>
       <c r="C13" s="0">
-        <v>0.1970231769227957</v>
+        <v>0.66296408016873964</v>
       </c>
       <c r="D13" s="0">
         <v>0.11718012076884676</v>
@@ -1087,7 +1286,7 @@
         <v>0.16114465884360851</v>
       </c>
       <c r="C14" s="0">
-        <v>0.088528661782977025</v>
+        <v>0.51956912338116601</v>
       </c>
       <c r="D14" s="0">
         <v>0.12524731932837119</v>
@@ -1105,25 +1304,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="12.453125" customWidth="true"/>
-    <col min="3" max="3" width="12.453125" customWidth="true"/>
-    <col min="4" max="4" width="12.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
     <col min="5" max="5" width="12.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1137,7 +1336,7 @@
         <v>0.56645793342000872</v>
       </c>
       <c r="C2" s="0">
-        <v>0.16961040258220378</v>
+        <v>0.1679837152354782</v>
       </c>
       <c r="D2" s="0">
         <v>0.27913923107813238</v>
@@ -1154,7 +1353,7 @@
         <v>0.68374833759842446</v>
       </c>
       <c r="C3" s="0">
-        <v>0.64158671588160687</v>
+        <v>0.62650335780909627</v>
       </c>
       <c r="D3" s="0">
         <v>0.62866322796012997</v>
@@ -1171,7 +1370,7 @@
         <v>0.83253653351281021</v>
       </c>
       <c r="C4" s="0">
-        <v>1.0255588486790448</v>
+        <v>1.0035089010902936</v>
       </c>
       <c r="D4" s="0">
         <v>0.97927444156147359</v>
@@ -1188,7 +1387,7 @@
         <v>1.0360814703366825</v>
       </c>
       <c r="C5" s="0">
-        <v>1.2696234367234949</v>
+        <v>1.1895925603145583</v>
       </c>
       <c r="D5" s="0">
         <v>1.2755619523573429</v>
@@ -1205,7 +1404,7 @@
         <v>1.1993458894654954</v>
       </c>
       <c r="C6" s="0">
-        <v>1.3763766285575505</v>
+        <v>1.252434345172609</v>
       </c>
       <c r="D6" s="0">
         <v>1.4832971168818632</v>
@@ -1222,7 +1421,7 @@
         <v>1.2459810374763192</v>
       </c>
       <c r="C7" s="0">
-        <v>1.4380754525899462</v>
+        <v>1.2407009705663441</v>
       </c>
       <c r="D7" s="0">
         <v>1.5622791621636074</v>
@@ -1239,7 +1438,7 @@
         <v>1.1663271879219781</v>
       </c>
       <c r="C8" s="0">
-        <v>1.3674817941869719</v>
+        <v>1.2107803475030869</v>
       </c>
       <c r="D8" s="0">
         <v>1.5514282198417895</v>
@@ -1256,7 +1455,7 @@
         <v>1.0059391755468183</v>
       </c>
       <c r="C9" s="0">
-        <v>1.2484696790411649</v>
+        <v>1.1180936887022808</v>
       </c>
       <c r="D9" s="0">
         <v>1.4521745301367883</v>
@@ -1273,7 +1472,7 @@
         <v>0.83341503652079718</v>
       </c>
       <c r="C10" s="0">
-        <v>1.102476554936908</v>
+        <v>0.98562145936125656</v>
       </c>
       <c r="D10" s="0">
         <v>1.3259303350079588</v>
@@ -1290,7 +1489,7 @@
         <v>0.70785379262645365</v>
       </c>
       <c r="C11" s="0">
-        <v>0.94403196411908064</v>
+        <v>0.84695678226945526</v>
       </c>
       <c r="D11" s="0">
         <v>1.1965065371744072</v>
@@ -1307,7 +1506,7 @@
         <v>0.63829890264006472</v>
       </c>
       <c r="C12" s="0">
-        <v>0.87567064687311402</v>
+        <v>0.8180318850141084</v>
       </c>
       <c r="D12" s="0">
         <v>1.0951205228844281</v>
@@ -1324,7 +1523,7 @@
         <v>0.64780078406458907</v>
       </c>
       <c r="C13" s="0">
-        <v>0.99255317541282106</v>
+        <v>0.83585118851254181</v>
       </c>
       <c r="D13" s="0">
         <v>1.044260573842432</v>
@@ -1341,7 +1540,7 @@
         <v>0.68094800557928392</v>
       </c>
       <c r="C14" s="0">
-        <v>0.91826507519332379</v>
+        <v>0.82138479793964558</v>
       </c>
       <c r="D14" s="0">
         <v>1.0870645493448594</v>
@@ -1359,25 +1558,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="12.453125" customWidth="true"/>
-    <col min="3" max="3" width="12.453125" customWidth="true"/>
-    <col min="4" max="4" width="13.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" customWidth="true"/>
     <col min="5" max="5" width="12.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1391,7 +1590,7 @@
         <v>0.18888583565545666</v>
       </c>
       <c r="C2" s="0">
-        <v>0.055056191403205675</v>
+        <v>0.054472937433764211</v>
       </c>
       <c r="D2" s="0">
         <v>0.095885094167423607</v>
@@ -1408,7 +1607,7 @@
         <v>0.24477868664357272</v>
       </c>
       <c r="C3" s="0">
-        <v>0.21942379625512387</v>
+        <v>0.21669427808708719</v>
       </c>
       <c r="D3" s="0">
         <v>0.20822880770250804</v>
@@ -1425,7 +1624,7 @@
         <v>0.30739909155665757</v>
       </c>
       <c r="C4" s="0">
-        <v>0.34911941762305521</v>
+        <v>0.34523645393770763</v>
       </c>
       <c r="D4" s="0">
         <v>0.31686311628029862</v>
@@ -1442,7 +1641,7 @@
         <v>0.38361458259296471</v>
       </c>
       <c r="C5" s="0">
-        <v>0.44523700173068809</v>
+        <v>0.41918952396377063</v>
       </c>
       <c r="D5" s="0">
         <v>0.40533616779110626</v>
@@ -1459,7 +1658,7 @@
         <v>0.45050058843907081</v>
       </c>
       <c r="C6" s="0">
-        <v>0.49460799796195437</v>
+        <v>0.46240295575508972</v>
       </c>
       <c r="D6" s="0">
         <v>0.46402501146273695</v>
@@ -1476,7 +1675,7 @@
         <v>0.47442416041066193</v>
       </c>
       <c r="C7" s="0">
-        <v>0.50888215758283761</v>
+        <v>0.43811680843408496</v>
       </c>
       <c r="D7" s="0">
         <v>0.47371289369094244</v>
@@ -1493,7 +1692,7 @@
         <v>0.4383410041273787</v>
       </c>
       <c r="C8" s="0">
-        <v>0.46088951851460042</v>
+        <v>0.42624211076970031</v>
       </c>
       <c r="D8" s="0">
         <v>0.45693705910257443</v>
@@ -1510,7 +1709,7 @@
         <v>0.36036872917389418</v>
       </c>
       <c r="C9" s="0">
-        <v>0.41124428101345317</v>
+        <v>0.38553769702723906</v>
       </c>
       <c r="D9" s="0">
         <v>0.41117536484811429</v>
@@ -1527,7 +1726,7 @@
         <v>0.27623482432252811</v>
       </c>
       <c r="C10" s="0">
-        <v>0.35240450239385895</v>
+        <v>0.34500558270740328</v>
       </c>
       <c r="D10" s="0">
         <v>0.36242505499151384</v>
@@ -1544,7 +1743,7 @@
         <v>0.21266295692677289</v>
       </c>
       <c r="C11" s="0">
-        <v>0.28884470890267849</v>
+        <v>0.29835717767124248</v>
       </c>
       <c r="D11" s="0">
         <v>0.32637204803066061</v>
@@ -1561,7 +1760,7 @@
         <v>0.17780375872910872</v>
       </c>
       <c r="C12" s="0">
-        <v>0.26923918250526707</v>
+        <v>0.29409205520579113</v>
       </c>
       <c r="D12" s="0">
         <v>0.30906681684373272</v>
@@ -1578,7 +1777,7 @@
         <v>0.18142309622065483</v>
       </c>
       <c r="C13" s="0">
-        <v>0.34494095170212885</v>
+        <v>0.29354924491872697</v>
       </c>
       <c r="D13" s="0">
         <v>0.30480811925622969</v>
@@ -1595,13 +1794,123 @@
         <v>0.19079860499112031</v>
       </c>
       <c r="C14" s="0">
-        <v>0.31820073969124218</v>
+        <v>0.30135306689724511</v>
       </c>
       <c r="D14" s="0">
         <v>0.32832923230015632</v>
       </c>
       <c r="E14" s="0">
         <v>0.49692783668915069</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" customWidth="true"/>
+    <col min="2" max="2" width="25.5703125" customWidth="true"/>
+    <col min="3" max="3" width="25.5703125" customWidth="true"/>
+    <col min="4" max="4" width="25.5703125" customWidth="true"/>
+    <col min="5" max="5" width="27.5703125" customWidth="true"/>
+    <col min="6" max="6" width="27.5703125" customWidth="true"/>
+    <col min="7" max="7" width="27.5703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0">
+        <v>1</v>
+      </c>
+      <c r="E2" s="0">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0.96599999999999997</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="0">
+        <v>0</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0</v>
+      </c>
+      <c r="D3" s="0">
+        <v>0.033000000000000002</v>
+      </c>
+      <c r="E3" s="0">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.097000000000000003</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="0">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="F4" s="0">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1613,25 +1922,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="15.453125" customWidth="true"/>
-    <col min="3" max="3" width="15.453125" customWidth="true"/>
-    <col min="4" max="4" width="15.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1645,7 +1954,7 @@
         <v>0.61760533023289943</v>
       </c>
       <c r="C2" s="0">
-        <v>0.014320932167651561</v>
+        <v>0.034444556112206502</v>
       </c>
       <c r="D2" s="0">
         <v>0.025836374268534339</v>
@@ -1662,7 +1971,7 @@
         <v>0.27401066406502445</v>
       </c>
       <c r="C3" s="0">
-        <v>0.078633810866388973</v>
+        <v>0.15860297193823761</v>
       </c>
       <c r="D3" s="0">
         <v>0.047436224533434102</v>
@@ -1679,7 +1988,7 @@
         <v>0.48572584118676537</v>
       </c>
       <c r="C4" s="0">
-        <v>0.00063720348609035257</v>
+        <v>0.02281304071027972</v>
       </c>
       <c r="D4" s="0">
         <v>0.0023829533643045277</v>
@@ -1696,7 +2005,7 @@
         <v>0.37896023257076389</v>
       </c>
       <c r="C5" s="0">
-        <v>7.2943369584228303e-05</v>
+        <v>0.008899451746967978</v>
       </c>
       <c r="D5" s="0">
         <v>0.00087028761071691744</v>
@@ -1713,7 +2022,7 @@
         <v>0.16844098588540335</v>
       </c>
       <c r="C6" s="0">
-        <v>3.0492063606523045e-06</v>
+        <v>0.00034705230453133731</v>
       </c>
       <c r="D6" s="0">
         <v>0.00028800680355986209</v>
@@ -1730,7 +2039,7 @@
         <v>0.18865950839443507</v>
       </c>
       <c r="C7" s="0">
-        <v>7.4257847594773843e-10</v>
+        <v>5.1501154952018141e-06</v>
       </c>
       <c r="D7" s="0">
         <v>1.7313704545100471e-06</v>
@@ -1747,7 +2056,7 @@
         <v>0.11264281749620113</v>
       </c>
       <c r="C8" s="0">
-        <v>2.5889214040835657e-10</v>
+        <v>5.2337761111001762e-05</v>
       </c>
       <c r="D8" s="0">
         <v>9.1825360658553663e-08</v>
@@ -1764,7 +2073,7 @@
         <v>0.0082348970463719477</v>
       </c>
       <c r="C9" s="0">
-        <v>2.7623122407636781e-12</v>
+        <v>4.2176566559314384e-06</v>
       </c>
       <c r="D9" s="0">
         <v>4.1066033057021658e-07</v>
@@ -1781,7 +2090,7 @@
         <v>0.0054650234312250742</v>
       </c>
       <c r="C10" s="0">
-        <v>1.3840770370442762e-10</v>
+        <v>0.00034149174991104697</v>
       </c>
       <c r="D10" s="0">
         <v>2.5877185318229478e-05</v>
@@ -1798,7 +2107,7 @@
         <v>0.00066881472126562383</v>
       </c>
       <c r="C11" s="0">
-        <v>1.7373651779300631e-07</v>
+        <v>0.0034767522055977268</v>
       </c>
       <c r="D11" s="0">
         <v>0.0019137543165940944</v>
@@ -1815,7 +2124,7 @@
         <v>0.00010616479047899098</v>
       </c>
       <c r="C12" s="0">
-        <v>8.8991479919566731e-07</v>
+        <v>0.0056164518770271928</v>
       </c>
       <c r="D12" s="0">
         <v>0.024721687652946581</v>
@@ -1832,7 +2141,7 @@
         <v>3.5062908573872787e-06</v>
       </c>
       <c r="C13" s="0">
-        <v>1.3647562361920685e-08</v>
+        <v>0.085441791387548371</v>
       </c>
       <c r="D13" s="0">
         <v>0.099175662356202884</v>
@@ -1849,7 +2158,7 @@
         <v>5.2235282347332347e-05</v>
       </c>
       <c r="C14" s="0">
-        <v>0.00025506246102925564</v>
+        <v>0.050642494068408379</v>
       </c>
       <c r="D14" s="0">
         <v>0.025426524320007103</v>
@@ -1867,25 +2176,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="12.453125" customWidth="true"/>
-    <col min="3" max="3" width="11.453125" customWidth="true"/>
-    <col min="4" max="4" width="11.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="11.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1899,7 +2208,7 @@
         <v>0.74020261176144553</v>
       </c>
       <c r="C2" s="0">
-        <v>1.673450199649168</v>
+        <v>1.5336895236345123</v>
       </c>
       <c r="D2" s="0">
         <v>1.4440969626615074</v>
@@ -1916,7 +2225,7 @@
         <v>0.97096890704918715</v>
       </c>
       <c r="C3" s="0">
-        <v>1.2468123465517984</v>
+        <v>1.0996958454837389</v>
       </c>
       <c r="D3" s="0">
         <v>1.3387601597193344</v>
@@ -1933,7 +2242,7 @@
         <v>0.81838846508768437</v>
       </c>
       <c r="C4" s="0">
-        <v>1.9663597848150165</v>
+        <v>1.4651793487860167</v>
       </c>
       <c r="D4" s="0">
         <v>1.7986121491619631</v>
@@ -1950,7 +2259,7 @@
         <v>0.89076855835267599</v>
       </c>
       <c r="C5" s="0">
-        <v>2.2115824640291168</v>
+        <v>1.6145440396135229</v>
       </c>
       <c r="D5" s="0">
         <v>1.9275693004963792</v>
@@ -1967,7 +2276,7 @@
         <v>1.0865837048433566</v>
       </c>
       <c r="C6" s="0">
-        <v>2.536903827910205</v>
+        <v>2.0373444465812938</v>
       </c>
       <c r="D6" s="0">
         <v>2.0596311866574153</v>
@@ -1984,7 +2293,7 @@
         <v>1.0645531520566243</v>
       </c>
       <c r="C7" s="0">
-        <v>3.2291917488781459</v>
+        <v>2.4862695491450117</v>
       </c>
       <c r="D7" s="0">
         <v>2.5918754868357357</v>
@@ -2001,7 +2310,7 @@
         <v>1.1733161733161737</v>
       </c>
       <c r="C8" s="0">
-        <v>3.3093093093093087</v>
+        <v>2.2473902473902472</v>
       </c>
       <c r="D8" s="0">
         <v>2.8511368511368502</v>
@@ -2018,7 +2327,7 @@
         <v>1.61978825522645</v>
       </c>
       <c r="C9" s="0">
-        <v>3.6210091207283286</v>
+        <v>2.5027180587844589</v>
       </c>
       <c r="D9" s="0">
         <v>2.7151066713241865</v>
@@ -2035,7 +2344,7 @@
         <v>1.6829228148195527</v>
       </c>
       <c r="C10" s="0">
-        <v>3.3519745844015678</v>
+        <v>2.0378755618980122</v>
       </c>
       <c r="D10" s="0">
         <v>2.3244951598062875</v>
@@ -2052,7 +2361,7 @@
         <v>1.9553843695133288</v>
       </c>
       <c r="C11" s="0">
-        <v>2.7880343070808196</v>
+        <v>1.744535917580917</v>
       </c>
       <c r="D11" s="0">
         <v>1.8264579275673956</v>
@@ -2069,7 +2378,7 @@
         <v>2.1696318119492624</v>
       </c>
       <c r="C12" s="0">
-        <v>2.6462089256413437</v>
+        <v>1.6738206443413512</v>
       </c>
       <c r="D12" s="0">
         <v>1.4480494876627501</v>
@@ -2086,7 +2395,7 @@
         <v>2.5142568693237743</v>
       </c>
       <c r="C13" s="0">
-        <v>2.9977858438197318</v>
+        <v>1.2281292025994892</v>
       </c>
       <c r="D13" s="0">
         <v>1.1949872230996048</v>
@@ -2103,7 +2412,7 @@
         <v>2.2441984799049308</v>
       </c>
       <c r="C14" s="0">
-        <v>2.065797443683647</v>
+        <v>1.3257457058277033</v>
       </c>
       <c r="D14" s="0">
         <v>1.44259598022601</v>
@@ -2121,25 +2430,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="12.453125" customWidth="true"/>
-    <col min="3" max="3" width="12.453125" customWidth="true"/>
-    <col min="4" max="4" width="12.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
     <col min="5" max="5" width="12.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2153,7 +2462,7 @@
         <v>0.16015465768799103</v>
       </c>
       <c r="C2" s="0">
-        <v>0.90762262262262261</v>
+        <v>0.79575825825825841</v>
       </c>
       <c r="D2" s="0">
         <v>0.50505721479054821</v>
@@ -2170,7 +2479,7 @@
         <v>0.15101801801801801</v>
       </c>
       <c r="C3" s="0">
-        <v>0.52134484484484489</v>
+        <v>0.38835485485485494</v>
       </c>
       <c r="D3" s="0">
         <v>0.45714664664664667</v>
@@ -2187,7 +2496,7 @@
         <v>0.15159260518380016</v>
       </c>
       <c r="C4" s="0">
-        <v>1.4171666509276579</v>
+        <v>0.67179548731121053</v>
       </c>
       <c r="D4" s="0">
         <v>0.88759362507161221</v>
@@ -2204,7 +2513,7 @@
         <v>0.18617609275942601</v>
       </c>
       <c r="C5" s="0">
-        <v>2.6097497433330767</v>
+        <v>1.0831128949462281</v>
       </c>
       <c r="D5" s="0">
         <v>1.1927328033161371</v>
@@ -2221,7 +2530,7 @@
         <v>0.28243431666961072</v>
       </c>
       <c r="C6" s="0">
-        <v>3.8406905140434553</v>
+        <v>1.9614326679620799</v>
       </c>
       <c r="D6" s="0">
         <v>1.5105909438850613</v>
@@ -2238,7 +2547,7 @@
         <v>0.30693076409743064</v>
       </c>
       <c r="C7" s="0">
-        <v>4.9537812145478801</v>
+        <v>2.3403721855188508</v>
       </c>
       <c r="D7" s="0">
         <v>2.0604970503837174</v>
@@ -2255,7 +2564,7 @@
         <v>0.40072151062627254</v>
       </c>
       <c r="C8" s="0">
-        <v>4.8899183809659998</v>
+        <v>1.911840262030738</v>
       </c>
       <c r="D8" s="0">
         <v>2.2283001709192178</v>
@@ -2272,7 +2581,7 @@
         <v>0.57712875375375394</v>
       </c>
       <c r="C9" s="0">
-        <v>4.7174685935935905</v>
+        <v>1.844060497997998</v>
       </c>
       <c r="D9" s="0">
         <v>2.0533987737737744</v>
@@ -2289,7 +2598,7 @@
         <v>0.86436131166627606</v>
       </c>
       <c r="C10" s="0">
-        <v>3.939737134297419</v>
+        <v>1.4191883301741461</v>
       </c>
       <c r="D10" s="0">
         <v>1.6329147374324682</v>
@@ -2306,7 +2615,7 @@
         <v>1.0591389389389387</v>
       </c>
       <c r="C11" s="0">
-        <v>3.143455455455455</v>
+        <v>0.94586106106106127</v>
       </c>
       <c r="D11" s="0">
         <v>1.0645101101101095</v>
@@ -2323,7 +2632,7 @@
         <v>1.2757860108170185</v>
       </c>
       <c r="C12" s="0">
-        <v>2.9381334512807387</v>
+        <v>0.78555605993590483</v>
       </c>
       <c r="D12" s="0">
         <v>0.61183796975269855</v>
@@ -2340,7 +2649,7 @@
         <v>1.4351481155952701</v>
       </c>
       <c r="C13" s="0">
-        <v>3.4997546001285844</v>
+        <v>0.54708334350610788</v>
       </c>
       <c r="D13" s="0">
         <v>0.41481329296776448</v>
@@ -2357,7 +2666,7 @@
         <v>1.4410207900207896</v>
       </c>
       <c r="C14" s="0">
-        <v>1.9492605682605679</v>
+        <v>0.52295456995456979</v>
       </c>
       <c r="D14" s="0">
         <v>0.38408701008701007</v>
@@ -2375,25 +2684,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="12.08984375" customWidth="true"/>
-    <col min="3" max="3" width="2.7265625" customWidth="true"/>
-    <col min="4" max="4" width="11.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="12.42578125" customWidth="true"/>
+    <col min="3" max="3" width="3" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="5.08984375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2577,25 +2886,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="11.453125" customWidth="true"/>
-    <col min="3" max="3" width="2.7265625" customWidth="true"/>
-    <col min="4" max="4" width="11.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="3" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="5.08984375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2779,25 +3088,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="15.08984375" customWidth="true"/>
-    <col min="3" max="3" width="2.7265625" customWidth="true"/>
-    <col min="4" max="4" width="15.08984375" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="15.5703125" customWidth="true"/>
+    <col min="3" max="3" width="3" customWidth="true"/>
+    <col min="4" max="4" width="15.5703125" customWidth="true"/>
     <col min="5" max="5" width="5.08984375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2981,25 +3290,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="15.08984375" customWidth="true"/>
-    <col min="3" max="3" width="2.7265625" customWidth="true"/>
-    <col min="4" max="4" width="15.08984375" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="15.5703125" customWidth="true"/>
+    <col min="3" max="3" width="3" customWidth="true"/>
+    <col min="4" max="4" width="15.5703125" customWidth="true"/>
     <col min="5" max="5" width="5.08984375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3183,25 +3492,25 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" customWidth="true"/>
-    <col min="2" max="2" width="11.453125" customWidth="true"/>
-    <col min="3" max="3" width="11.453125" customWidth="true"/>
-    <col min="4" max="4" width="11.453125" customWidth="true"/>
+    <col min="1" max="1" width="7.85546875" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="11.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3215,7 +3524,7 @@
         <v>3.2611214789639313</v>
       </c>
       <c r="C2" s="0">
-        <v>8.5662277205852568</v>
+        <v>9.974381445021212</v>
       </c>
       <c r="D2" s="0">
         <v>5.8185486540013702</v>
@@ -3232,7 +3541,7 @@
         <v>3.6458970310794339</v>
       </c>
       <c r="C3" s="0">
-        <v>5.0864215114371998</v>
+        <v>4.4385055888523066</v>
       </c>
       <c r="D3" s="0">
         <v>7.7449740536156311</v>
@@ -3249,7 +3558,7 @@
         <v>3.6192594303025749</v>
       </c>
       <c r="C4" s="0">
-        <v>8.5928793940479977</v>
+        <v>7.1508145507835081</v>
       </c>
       <c r="D4" s="0">
         <v>8.7905577328913882</v>
@@ -3266,7 +3575,7 @@
         <v>2.8354077331237546</v>
       </c>
       <c r="C5" s="0">
-        <v>8.0496997801052217</v>
+        <v>8.0349533194253873</v>
       </c>
       <c r="D5" s="0">
         <v>6.8471783334848215</v>
@@ -3283,7 +3592,7 @@
         <v>1.9192001867098385</v>
       </c>
       <c r="C6" s="0">
-        <v>6.7397651977468254</v>
+        <v>6.6306018079982678</v>
       </c>
       <c r="D6" s="0">
         <v>6.3598547741453011</v>
@@ -3300,7 +3609,7 @@
         <v>2.91789068815909</v>
       </c>
       <c r="C7" s="0">
-        <v>6.7332412069906287</v>
+        <v>6.6359314644677152</v>
       </c>
       <c r="D7" s="0">
         <v>5.411967904524567</v>
@@ -3317,7 +3626,7 @@
         <v>3.7306349216300383</v>
       </c>
       <c r="C8" s="0">
-        <v>6.653783312521508</v>
+        <v>7.5513340545422425</v>
       </c>
       <c r="D8" s="0">
         <v>4.30418038698435</v>
@@ -3334,7 +3643,7 @@
         <v>5.1874321561457437</v>
       </c>
       <c r="C9" s="0">
-        <v>6.7195679612482824</v>
+        <v>6.4057179467690482</v>
       </c>
       <c r="D9" s="0">
         <v>3.8952432055775441</v>
@@ -3351,7 +3660,7 @@
         <v>6.728737869462841</v>
       </c>
       <c r="C10" s="0">
-        <v>5.3148571315708324</v>
+        <v>4.9139121523609317</v>
       </c>
       <c r="D10" s="0">
         <v>3.2912492534791205</v>
@@ -3368,7 +3677,7 @@
         <v>8.4587080037655848</v>
       </c>
       <c r="C11" s="0">
-        <v>3.3907802688421018</v>
+        <v>3.1932905514201151</v>
       </c>
       <c r="D11" s="0">
         <v>3.9856300418531525</v>
@@ -3385,7 +3694,7 @@
         <v>9.1887996967036685</v>
       </c>
       <c r="C12" s="0">
-        <v>2.7890884282039634</v>
+        <v>3.6656995525416329</v>
       </c>
       <c r="D12" s="0">
         <v>5.4656044118402711</v>
@@ -3402,7 +3711,7 @@
         <v>7.7343243752311803</v>
       </c>
       <c r="C13" s="0">
-        <v>4.904435061250858</v>
+        <v>3.168181664250092</v>
       </c>
       <c r="D13" s="0">
         <v>6.351802400068089</v>
@@ -3419,7 +3728,7 @@
         <v>5.7169112274721439</v>
       </c>
       <c r="C14" s="0">
-        <v>4.7198621914521359</v>
+        <v>3.7161563688265318</v>
       </c>
       <c r="D14" s="0">
         <v>5.566329221892925</v>

--- a/IaR_GaR_April_2026/Outputs/forecast_evaluation/comparison_fcst_eval_growth.xlsx
+++ b/IaR_GaR_April_2026/Outputs/forecast_evaluation/comparison_fcst_eval_growth.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="127">
   <si>
     <t>horizon</t>
   </si>
@@ -240,6 +240,174 @@
   </si>
   <si>
     <t>GMM_CVM_std_bonf_w_wi_3</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
   </si>
 </sst>
 </file>
@@ -297,16 +465,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -551,16 +719,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -805,16 +973,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1059,16 +1227,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1313,16 +1481,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1567,16 +1735,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1931,16 +2099,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2185,16 +2353,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2439,16 +2607,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2693,16 +2861,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2895,16 +3063,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3097,16 +3265,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3299,16 +3467,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3501,16 +3669,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>

--- a/IaR_GaR_April_2026/Outputs/forecast_evaluation/comparison_fcst_eval_growth.xlsx
+++ b/IaR_GaR_April_2026/Outputs/forecast_evaluation/comparison_fcst_eval_growth.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="193">
   <si>
     <t>horizon</t>
   </si>
@@ -408,6 +408,204 @@
   </si>
   <si>
     <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>fanchart</t>
+  </si>
+  <si>
+    <t>qr</t>
+  </si>
+  <si>
+    <t>bvar</t>
+  </si>
+  <si>
+    <t>GMM_KS_std_bonf_w_wi_1</t>
+  </si>
+  <si>
+    <t>GMM_KS_std_bonf_w_wi_2</t>
+  </si>
+  <si>
+    <t>GMM_KS_std_bonf_w_wi_3</t>
+  </si>
+  <si>
+    <t>GMM_CVM_std_bonf_w_wi_1</t>
+  </si>
+  <si>
+    <t>GMM_CVM_std_bonf_w_wi_2</t>
+  </si>
+  <si>
+    <t>GMM_CVM_std_bonf_w_wi_3</t>
   </si>
 </sst>
 </file>
@@ -465,16 +663,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -491,7 +689,7 @@
         <v>0.19042743907996229</v>
       </c>
       <c r="D2" s="0">
-        <v>0.19528968220564347</v>
+        <v>0.19872237201324139</v>
       </c>
       <c r="E2" s="0">
         <v>0.15591199773247905</v>
@@ -508,7 +706,7 @@
         <v>0.1504135714879189</v>
       </c>
       <c r="D3" s="0">
-        <v>0.18277082151778923</v>
+        <v>0.10712541201019532</v>
       </c>
       <c r="E3" s="0">
         <v>0.27295529855764578</v>
@@ -525,7 +723,7 @@
         <v>0.20169170657447</v>
       </c>
       <c r="D4" s="0">
-        <v>0.24742932092734116</v>
+        <v>0.13555703999015145</v>
       </c>
       <c r="E4" s="0">
         <v>0.34750008907715058</v>
@@ -542,7 +740,7 @@
         <v>0.22397972850475989</v>
       </c>
       <c r="D5" s="0">
-        <v>0.26778041316153073</v>
+        <v>0.10144397192505794</v>
       </c>
       <c r="E5" s="0">
         <v>0.35925314693549149</v>
@@ -559,7 +757,7 @@
         <v>0.28594408866230941</v>
       </c>
       <c r="D6" s="0">
-        <v>0.28900685160468542</v>
+        <v>0.1182617078629899</v>
       </c>
       <c r="E6" s="0">
         <v>0.41659379434822996</v>
@@ -576,7 +774,7 @@
         <v>0.35199484598127867</v>
       </c>
       <c r="D7" s="0">
-        <v>0.36659949568749228</v>
+        <v>0.1708827942298406</v>
       </c>
       <c r="E7" s="0">
         <v>0.56496203003384826</v>
@@ -593,7 +791,7 @@
         <v>0.32187935206638957</v>
       </c>
       <c r="D8" s="0">
-        <v>0.40732985329200311</v>
+        <v>0.20344751165240638</v>
       </c>
       <c r="E8" s="0">
         <v>0.57394609820231468</v>
@@ -610,7 +808,7 @@
         <v>0.36187354213386153</v>
       </c>
       <c r="D9" s="0">
-        <v>0.39279924721648096</v>
+        <v>0.22127373203268186</v>
       </c>
       <c r="E9" s="0">
         <v>0.55262569690000662</v>
@@ -627,7 +825,7 @@
         <v>0.2978827399962517</v>
       </c>
       <c r="D10" s="0">
-        <v>0.33929752641304667</v>
+        <v>0.18640164647697341</v>
       </c>
       <c r="E10" s="0">
         <v>0.53854002133050705</v>
@@ -644,7 +842,7 @@
         <v>0.26042813027814826</v>
       </c>
       <c r="D11" s="0">
-        <v>0.27238711624176359</v>
+        <v>0.23963330288479226</v>
       </c>
       <c r="E11" s="0">
         <v>0.43232379483671357</v>
@@ -661,7 +859,7 @@
         <v>0.25603354211073448</v>
       </c>
       <c r="D12" s="0">
-        <v>0.22139964042730431</v>
+        <v>0.26642939342032113</v>
       </c>
       <c r="E12" s="0">
         <v>0.39229897896382715</v>
@@ -678,7 +876,7 @@
         <v>0.19197662244303593</v>
       </c>
       <c r="D13" s="0">
-        <v>0.18738247268664709</v>
+        <v>0.25363320059758288</v>
       </c>
       <c r="E13" s="0">
         <v>0.37313397830086764</v>
@@ -695,7 +893,7 @@
         <v>0.21241242933645166</v>
       </c>
       <c r="D14" s="0">
-        <v>0.23146430357573189</v>
+        <v>0.25459506983989766</v>
       </c>
       <c r="E14" s="0">
         <v>0.48590913364244048</v>
@@ -713,22 +911,22 @@
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="13.7109375" customWidth="true"/>
-    <col min="4" max="4" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -745,7 +943,7 @@
         <v>0.040861441346580096</v>
       </c>
       <c r="D2" s="0">
-        <v>0.21311516804565189</v>
+        <v>0.18079793700867575</v>
       </c>
       <c r="E2" s="0">
         <v>0.68831213837965133</v>
@@ -762,7 +960,7 @@
         <v>0.3499015278032358</v>
       </c>
       <c r="D3" s="0">
-        <v>0.10137968663420716</v>
+        <v>0.30978646174982716</v>
       </c>
       <c r="E3" s="0">
         <v>0.22544002930494411</v>
@@ -779,7 +977,7 @@
         <v>0.12812978817280407</v>
       </c>
       <c r="D4" s="0">
-        <v>0.066553138230247111</v>
+        <v>0.27597770764792551</v>
       </c>
       <c r="E4" s="0">
         <v>0.28818793523641051</v>
@@ -796,7 +994,7 @@
         <v>0.090306168490604466</v>
       </c>
       <c r="D5" s="0">
-        <v>0.144187928461464</v>
+        <v>0.30158974566396723</v>
       </c>
       <c r="E5" s="0">
         <v>0.062855343373911632</v>
@@ -813,7 +1011,7 @@
         <v>0.1567451803233213</v>
       </c>
       <c r="D6" s="0">
-        <v>0.173837641152077</v>
+        <v>0.31364761021731735</v>
       </c>
       <c r="E6" s="0">
         <v>0.07068156475293097</v>
@@ -830,7 +1028,7 @@
         <v>0.15642457466498805</v>
       </c>
       <c r="D7" s="0">
-        <v>0.24757662359272214</v>
+        <v>0.32050032912016291</v>
       </c>
       <c r="E7" s="0">
         <v>0.0096007437802668738</v>
@@ -847,7 +1045,7 @@
         <v>0.10946686573774889</v>
       </c>
       <c r="D8" s="0">
-        <v>0.36640191956100954</v>
+        <v>0.46310665488967573</v>
       </c>
       <c r="E8" s="0">
         <v>0.0041022074669080366</v>
@@ -864,7 +1062,7 @@
         <v>0.17082870123571225</v>
       </c>
       <c r="D9" s="0">
-        <v>0.42036874274727265</v>
+        <v>0.45156480242670283</v>
       </c>
       <c r="E9" s="0">
         <v>0.0039342356736554729</v>
@@ -881,7 +1079,7 @@
         <v>0.29624524980235356</v>
       </c>
       <c r="D10" s="0">
-        <v>0.5103199303494883</v>
+        <v>0.50531215314252376</v>
       </c>
       <c r="E10" s="0">
         <v>0.013587201663587956</v>
@@ -898,7 +1096,7 @@
         <v>0.5260153193748236</v>
       </c>
       <c r="D11" s="0">
-        <v>0.40795410531987608</v>
+        <v>0.50242160401569147</v>
       </c>
       <c r="E11" s="0">
         <v>0.036188908936314323</v>
@@ -915,7 +1113,7 @@
         <v>0.45313436626608816</v>
       </c>
       <c r="D12" s="0">
-        <v>0.24276946426442847</v>
+        <v>0.17612139611675115</v>
       </c>
       <c r="E12" s="0">
         <v>0.039858372347144955</v>
@@ -932,7 +1130,7 @@
         <v>0.53008543088784188</v>
       </c>
       <c r="D13" s="0">
-        <v>0.17437083556969757</v>
+        <v>0.39089006678185068</v>
       </c>
       <c r="E13" s="0">
         <v>0.015058227979301897</v>
@@ -949,7 +1147,7 @@
         <v>0.44578043386097388</v>
       </c>
       <c r="D14" s="0">
-        <v>0.23396031947262286</v>
+        <v>0.38007983534902268</v>
       </c>
       <c r="E14" s="0">
         <v>0.023249768241102586</v>
@@ -973,16 +1171,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -999,7 +1197,7 @@
         <v>15.82192835928117</v>
       </c>
       <c r="D2" s="0">
-        <v>4.0032542743264541</v>
+        <v>4.781957802566505</v>
       </c>
       <c r="E2" s="0">
         <v>5.6345185290204354</v>
@@ -1016,7 +1214,7 @@
         <v>10.46746225873884</v>
       </c>
       <c r="D3" s="0">
-        <v>6.9213533452461649</v>
+        <v>7.8289441251201408</v>
       </c>
       <c r="E3" s="0">
         <v>5.8108121299644804</v>
@@ -1033,7 +1231,7 @@
         <v>9.5495873928723984</v>
       </c>
       <c r="D4" s="0">
-        <v>9.4342579176117898</v>
+        <v>5.052362894059697</v>
       </c>
       <c r="E4" s="0">
         <v>4.3791804766078233</v>
@@ -1050,7 +1248,7 @@
         <v>9.3414550872306528</v>
       </c>
       <c r="D5" s="0">
-        <v>6.7972159573074356</v>
+        <v>7.199010558360297</v>
       </c>
       <c r="E5" s="0">
         <v>9.986218998589381</v>
@@ -1067,7 +1265,7 @@
         <v>4.7194310605114298</v>
       </c>
       <c r="D6" s="0">
-        <v>9.0585344351617341</v>
+        <v>4.8047262952404886</v>
       </c>
       <c r="E6" s="0">
         <v>8.195951297559132</v>
@@ -1084,7 +1282,7 @@
         <v>6.8412602823854787</v>
       </c>
       <c r="D7" s="0">
-        <v>7.0538962357389439</v>
+        <v>5.8999011544917783</v>
       </c>
       <c r="E7" s="0">
         <v>16.830030008973527</v>
@@ -1101,7 +1299,7 @@
         <v>11.349975271077838</v>
       </c>
       <c r="D8" s="0">
-        <v>10.084045641856228</v>
+        <v>5.0913391681054181</v>
       </c>
       <c r="E8" s="0">
         <v>11.574472374073373</v>
@@ -1118,7 +1316,7 @@
         <v>7.1469607856794353</v>
       </c>
       <c r="D9" s="0">
-        <v>8.6037762696578586</v>
+        <v>7.8270578390721735</v>
       </c>
       <c r="E9" s="0">
         <v>13.248164803714937</v>
@@ -1135,7 +1333,7 @@
         <v>6.3892371751934274</v>
       </c>
       <c r="D10" s="0">
-        <v>6.5883295803771622</v>
+        <v>4.2673077236579182</v>
       </c>
       <c r="E10" s="0">
         <v>16.77007149986245</v>
@@ -1152,7 +1350,7 @@
         <v>5.4737174269237494</v>
       </c>
       <c r="D11" s="0">
-        <v>4.6954331884756968</v>
+        <v>4.5339288110797886</v>
       </c>
       <c r="E11" s="0">
         <v>9.5235415644985757</v>
@@ -1169,7 +1367,7 @@
         <v>2.7599610028432462</v>
       </c>
       <c r="D12" s="0">
-        <v>9.659520506900213</v>
+        <v>4.8893005182491596</v>
       </c>
       <c r="E12" s="0">
         <v>8.6934914039679629</v>
@@ -1186,7 +1384,7 @@
         <v>3.2404909078550901</v>
       </c>
       <c r="D13" s="0">
-        <v>8.8031042631781737</v>
+        <v>5.8348317265378586</v>
       </c>
       <c r="E13" s="0">
         <v>10.263900367645462</v>
@@ -1203,7 +1401,7 @@
         <v>4.2101798133626591</v>
       </c>
       <c r="D14" s="0">
-        <v>8.6192913236775937</v>
+        <v>4.4538969084145617</v>
       </c>
       <c r="E14" s="0">
         <v>13.403385961619186</v>
@@ -1221,22 +1419,22 @@
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="14.7109375" customWidth="true"/>
-    <col min="4" max="4" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1253,7 +1451,7 @@
         <v>0.0073713006231521661</v>
       </c>
       <c r="D2" s="0">
-        <v>0.54894750960427818</v>
+        <v>0.44306577034312533</v>
       </c>
       <c r="E2" s="0">
         <v>0.34342076316334647</v>
@@ -1270,7 +1468,7 @@
         <v>0.063022960106911774</v>
       </c>
       <c r="D3" s="0">
-        <v>0.22655538104628326</v>
+        <v>0.16591823478856416</v>
       </c>
       <c r="E3" s="0">
         <v>0.32506518980700383</v>
@@ -1287,7 +1485,7 @@
         <v>0.089050991537168112</v>
       </c>
       <c r="D4" s="0">
-        <v>0.092947178029276656</v>
+        <v>0.40952325840573534</v>
       </c>
       <c r="E4" s="0">
         <v>0.49620953346307051</v>
@@ -1304,7 +1502,7 @@
         <v>0.096195566385820719</v>
       </c>
       <c r="D5" s="0">
-        <v>0.23616371508040046</v>
+        <v>0.2062553869855861</v>
       </c>
       <c r="E5" s="0">
         <v>0.075626667730786079</v>
@@ -1321,7 +1519,7 @@
         <v>0.45107125756402067</v>
       </c>
       <c r="D6" s="0">
-        <v>0.10675207022273914</v>
+        <v>0.44017362950536276</v>
       </c>
       <c r="E6" s="0">
         <v>0.14576189389809269</v>
@@ -1338,7 +1536,7 @@
         <v>0.23271620589900577</v>
       </c>
       <c r="D7" s="0">
-        <v>0.21666273924739599</v>
+        <v>0.31608116880835879</v>
       </c>
       <c r="E7" s="0">
         <v>0.0048336893567137995</v>
@@ -1355,7 +1553,7 @@
         <v>0.044865966985496941</v>
       </c>
       <c r="D8" s="0">
-        <v>0.072888575834855418</v>
+        <v>0.40483512511510722</v>
       </c>
       <c r="E8" s="0">
         <v>0.041107364063473373</v>
@@ -1372,7 +1570,7 @@
         <v>0.20993808632549316</v>
       </c>
       <c r="D9" s="0">
-        <v>0.12595070325310753</v>
+        <v>0.16602789368219673</v>
       </c>
       <c r="E9" s="0">
         <v>0.021160928124125289</v>
@@ -1389,7 +1587,7 @@
         <v>0.27016473843792077</v>
       </c>
       <c r="D10" s="0">
-        <v>0.25310024952240395</v>
+        <v>0.51160647182243757</v>
       </c>
       <c r="E10" s="0">
         <v>0.0049571508387528107</v>
@@ -1406,7 +1604,7 @@
         <v>0.36083646851955975</v>
       </c>
       <c r="D11" s="0">
-        <v>0.45416818752724286</v>
+        <v>0.47535675437844516</v>
       </c>
       <c r="E11" s="0">
         <v>0.089917509329231149</v>
@@ -1423,7 +1621,7 @@
         <v>0.73693349696535093</v>
       </c>
       <c r="D12" s="0">
-        <v>0.085477826738126317</v>
+        <v>0.42953908225346549</v>
       </c>
       <c r="E12" s="0">
         <v>0.12193222683556937</v>
@@ -1440,7 +1638,7 @@
         <v>0.66296408016873964</v>
       </c>
       <c r="D13" s="0">
-        <v>0.11718012076884676</v>
+        <v>0.32262375451351932</v>
       </c>
       <c r="E13" s="0">
         <v>0.068093884634720658</v>
@@ -1457,7 +1655,7 @@
         <v>0.51956912338116601</v>
       </c>
       <c r="D14" s="0">
-        <v>0.12524731932837119</v>
+        <v>0.48607546972555882</v>
       </c>
       <c r="E14" s="0">
         <v>0.01987805158127931</v>
@@ -1481,16 +1679,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1507,7 +1705,7 @@
         <v>0.1679837152354782</v>
       </c>
       <c r="D2" s="0">
-        <v>0.27913923107813238</v>
+        <v>0.2809489921158797</v>
       </c>
       <c r="E2" s="0">
         <v>0.50647631546024863</v>
@@ -1524,7 +1722,7 @@
         <v>0.62650335780909627</v>
       </c>
       <c r="D3" s="0">
-        <v>0.62866322796012997</v>
+        <v>0.62167181402044225</v>
       </c>
       <c r="E3" s="0">
         <v>0.57095405101496277</v>
@@ -1541,7 +1739,7 @@
         <v>1.0035089010902936</v>
       </c>
       <c r="D4" s="0">
-        <v>0.97927444156147359</v>
+        <v>0.96072627215794892</v>
       </c>
       <c r="E4" s="0">
         <v>0.98155429835630481</v>
@@ -1558,7 +1756,7 @@
         <v>1.1895925603145583</v>
       </c>
       <c r="D5" s="0">
-        <v>1.2755619523573429</v>
+        <v>1.2458289507693914</v>
       </c>
       <c r="E5" s="0">
         <v>1.2713224172669342</v>
@@ -1575,7 +1773,7 @@
         <v>1.252434345172609</v>
       </c>
       <c r="D6" s="0">
-        <v>1.4832971168818632</v>
+        <v>1.4621751463874488</v>
       </c>
       <c r="E6" s="0">
         <v>1.302399546160403</v>
@@ -1592,7 +1790,7 @@
         <v>1.2407009705663441</v>
       </c>
       <c r="D7" s="0">
-        <v>1.5622791621636074</v>
+        <v>1.5555692831286236</v>
       </c>
       <c r="E7" s="0">
         <v>1.3713177621214958</v>
@@ -1609,7 +1807,7 @@
         <v>1.2107803475030869</v>
       </c>
       <c r="D8" s="0">
-        <v>1.5514282198417895</v>
+        <v>1.5703368015237504</v>
       </c>
       <c r="E8" s="0">
         <v>1.4450424410809661</v>
@@ -1626,7 +1824,7 @@
         <v>1.1180936887022808</v>
       </c>
       <c r="D9" s="0">
-        <v>1.4521745301367883</v>
+        <v>1.4819285520547654</v>
       </c>
       <c r="E9" s="0">
         <v>1.4551603297551585</v>
@@ -1643,7 +1841,7 @@
         <v>0.98562145936125656</v>
       </c>
       <c r="D10" s="0">
-        <v>1.3259303350079588</v>
+        <v>1.3502779223169923</v>
       </c>
       <c r="E10" s="0">
         <v>1.4439038888194222</v>
@@ -1660,7 +1858,7 @@
         <v>0.84695678226945526</v>
       </c>
       <c r="D11" s="0">
-        <v>1.1965065371744072</v>
+        <v>1.2450496235625037</v>
       </c>
       <c r="E11" s="0">
         <v>1.4255902921749017</v>
@@ -1677,7 +1875,7 @@
         <v>0.8180318850141084</v>
       </c>
       <c r="D12" s="0">
-        <v>1.0951205228844281</v>
+        <v>1.1846320830882715</v>
       </c>
       <c r="E12" s="0">
         <v>1.4562601751235482</v>
@@ -1694,7 +1892,7 @@
         <v>0.83585118851254181</v>
       </c>
       <c r="D13" s="0">
-        <v>1.044260573842432</v>
+        <v>1.1773074868025273</v>
       </c>
       <c r="E13" s="0">
         <v>1.5105726857697219</v>
@@ -1711,7 +1909,7 @@
         <v>0.82138479793964558</v>
       </c>
       <c r="D14" s="0">
-        <v>1.0870645493448594</v>
+        <v>1.2693980482630896</v>
       </c>
       <c r="E14" s="0">
         <v>1.5417742712901181</v>
@@ -1735,16 +1933,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -1761,7 +1959,7 @@
         <v>0.054472937433764211</v>
       </c>
       <c r="D2" s="0">
-        <v>0.095885094167423607</v>
+        <v>0.096757618588159608</v>
       </c>
       <c r="E2" s="0">
         <v>0.13478902349114597</v>
@@ -1778,7 +1976,7 @@
         <v>0.21669427808708719</v>
       </c>
       <c r="D3" s="0">
-        <v>0.20822880770250804</v>
+        <v>0.2068204529785985</v>
       </c>
       <c r="E3" s="0">
         <v>0.15939997405061687</v>
@@ -1795,7 +1993,7 @@
         <v>0.34523645393770763</v>
       </c>
       <c r="D4" s="0">
-        <v>0.31686311628029862</v>
+        <v>0.31266497930054438</v>
       </c>
       <c r="E4" s="0">
         <v>0.35159728555157344</v>
@@ -1812,7 +2010,7 @@
         <v>0.41918952396377063</v>
       </c>
       <c r="D5" s="0">
-        <v>0.40533616779110626</v>
+        <v>0.40576888828641622</v>
       </c>
       <c r="E5" s="0">
         <v>0.41301094073859773</v>
@@ -1829,7 +2027,7 @@
         <v>0.46240295575508972</v>
       </c>
       <c r="D6" s="0">
-        <v>0.46402501146273695</v>
+        <v>0.48328407036722948</v>
       </c>
       <c r="E6" s="0">
         <v>0.41613697888057966</v>
@@ -1846,7 +2044,7 @@
         <v>0.43811680843408496</v>
       </c>
       <c r="D7" s="0">
-        <v>0.47371289369094244</v>
+        <v>0.51964497287978684</v>
       </c>
       <c r="E7" s="0">
         <v>0.43981563109013577</v>
@@ -1863,7 +2061,7 @@
         <v>0.42624211076970031</v>
       </c>
       <c r="D8" s="0">
-        <v>0.45693705910257443</v>
+        <v>0.52664568312986693</v>
       </c>
       <c r="E8" s="0">
         <v>0.45997198127620509</v>
@@ -1880,7 +2078,7 @@
         <v>0.38553769702723906</v>
       </c>
       <c r="D9" s="0">
-        <v>0.41117536484811429</v>
+        <v>0.49472740887684474</v>
       </c>
       <c r="E9" s="0">
         <v>0.4461582129817111</v>
@@ -1897,7 +2095,7 @@
         <v>0.34500558270740328</v>
       </c>
       <c r="D10" s="0">
-        <v>0.36242505499151384</v>
+        <v>0.44504072880290957</v>
       </c>
       <c r="E10" s="0">
         <v>0.43009545178412523</v>
@@ -1914,7 +2112,7 @@
         <v>0.29835717767124248</v>
       </c>
       <c r="D11" s="0">
-        <v>0.32637204803066061</v>
+        <v>0.4133142033288022</v>
       </c>
       <c r="E11" s="0">
         <v>0.43572697137845473</v>
@@ -1931,7 +2129,7 @@
         <v>0.29409205520579113</v>
       </c>
       <c r="D12" s="0">
-        <v>0.30906681684373272</v>
+        <v>0.4046415413462488</v>
       </c>
       <c r="E12" s="0">
         <v>0.43804653191325599</v>
@@ -1948,7 +2146,7 @@
         <v>0.29354924491872697</v>
       </c>
       <c r="D13" s="0">
-        <v>0.30480811925622969</v>
+        <v>0.40914092952429637</v>
       </c>
       <c r="E13" s="0">
         <v>0.46073833193900054</v>
@@ -1965,7 +2163,7 @@
         <v>0.30135306689724511</v>
       </c>
       <c r="D14" s="0">
-        <v>0.32832923230015632</v>
+        <v>0.43839646255327341</v>
       </c>
       <c r="E14" s="0">
         <v>0.49692783668915069</v>
@@ -1991,79 +2189,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>65</v>
+        <v>187</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>67</v>
+        <v>189</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="B2" s="0">
-        <v>1</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="C2" s="0">
-        <v>1</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="D2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>0.99399999999999999</v>
+        <v>0.1208</v>
       </c>
       <c r="G2" s="0">
-        <v>0.96599999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>63</v>
+        <v>185</v>
       </c>
       <c r="B3" s="0">
         <v>0</v>
       </c>
       <c r="C3" s="0">
-        <v>0</v>
+        <v>0.0033999999999999998</v>
       </c>
       <c r="D3" s="0">
-        <v>0.033000000000000002</v>
+        <v>0.0014</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>0.64600000000000002</v>
+        <v>0.1232</v>
       </c>
       <c r="G3" s="0">
-        <v>0.097000000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>64</v>
+        <v>186</v>
       </c>
       <c r="B4" s="0">
-        <v>1</v>
+        <v>0.99360000000000004</v>
       </c>
       <c r="C4" s="0">
         <v>0</v>
@@ -2072,13 +2270,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="0">
-        <v>0.29199999999999998</v>
+        <v>0.0028</v>
       </c>
       <c r="F4" s="0">
         <v>0</v>
       </c>
       <c r="G4" s="0">
-        <v>0</v>
+        <v>0.073599999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2093,22 +2291,22 @@
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="15.7109375" customWidth="true"/>
     <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2125,7 +2323,7 @@
         <v>0.034444556112206502</v>
       </c>
       <c r="D2" s="0">
-        <v>0.025836374268534339</v>
+        <v>0.022143585642230523</v>
       </c>
       <c r="E2" s="0">
         <v>0.13136388183342543</v>
@@ -2142,7 +2340,7 @@
         <v>0.15860297193823761</v>
       </c>
       <c r="D3" s="0">
-        <v>0.047436224533434102</v>
+        <v>0.54143351646348525</v>
       </c>
       <c r="E3" s="0">
         <v>0.00047526262145239281</v>
@@ -2159,7 +2357,7 @@
         <v>0.02281304071027972</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0023829533643045277</v>
+        <v>0.26448283961355312</v>
       </c>
       <c r="E4" s="0">
         <v>2.6738093588918562e-06</v>
@@ -2176,7 +2374,7 @@
         <v>0.008899451746967978</v>
       </c>
       <c r="D5" s="0">
-        <v>0.00087028761071691744</v>
+        <v>0.63517887020697672</v>
       </c>
       <c r="E5" s="0">
         <v>1.0545816544463347e-06</v>
@@ -2193,7 +2391,7 @@
         <v>0.00034705230453133731</v>
       </c>
       <c r="D6" s="0">
-        <v>0.00028800680355986209</v>
+        <v>0.44940386528256104</v>
       </c>
       <c r="E6" s="0">
         <v>7.229193712909694e-09</v>
@@ -2210,7 +2408,7 @@
         <v>5.1501154952018141e-06</v>
       </c>
       <c r="D7" s="0">
-        <v>1.7313704545100471e-06</v>
+        <v>0.096318939092702671</v>
       </c>
       <c r="E7" s="0">
         <v>5.9591835039673681e-16</v>
@@ -2227,7 +2425,7 @@
         <v>5.2337761111001762e-05</v>
       </c>
       <c r="D8" s="0">
-        <v>9.1825360658553663e-08</v>
+        <v>0.029541082747840026</v>
       </c>
       <c r="E8" s="0">
         <v>1.8944119367510097e-16</v>
@@ -2244,7 +2442,7 @@
         <v>4.2176566559314384e-06</v>
       </c>
       <c r="D9" s="0">
-        <v>4.1066033057021658e-07</v>
+        <v>0.015095058111258908</v>
       </c>
       <c r="E9" s="0">
         <v>2.7913798375274149e-15</v>
@@ -2261,7 +2459,7 @@
         <v>0.00034149174991104697</v>
       </c>
       <c r="D10" s="0">
-        <v>2.5877185318229478e-05</v>
+        <v>0.066944843316253541</v>
       </c>
       <c r="E10" s="0">
         <v>1.561155258508762e-14</v>
@@ -2278,7 +2476,7 @@
         <v>0.0034767522055977268</v>
       </c>
       <c r="D11" s="0">
-        <v>0.0019137543165940944</v>
+        <v>0.0092112557223408657</v>
       </c>
       <c r="E11" s="0">
         <v>2.3688754290922974e-09</v>
@@ -2295,7 +2493,7 @@
         <v>0.0056164518770271928</v>
       </c>
       <c r="D12" s="0">
-        <v>0.024721687652946581</v>
+        <v>0.0034518378058760167</v>
       </c>
       <c r="E12" s="0">
         <v>1.2211103456711071e-07</v>
@@ -2312,7 +2510,7 @@
         <v>0.085441791387548371</v>
       </c>
       <c r="D13" s="0">
-        <v>0.099175662356202884</v>
+        <v>0.0081450867665097543</v>
       </c>
       <c r="E13" s="0">
         <v>7.8952503682134265e-07</v>
@@ -2329,7 +2527,7 @@
         <v>0.050642494068408379</v>
       </c>
       <c r="D14" s="0">
-        <v>0.025426524320007103</v>
+        <v>0.010173355617100789</v>
       </c>
       <c r="E14" s="0">
         <v>4.4677009184411504e-11</v>
@@ -2347,22 +2545,22 @@
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="12.7109375" customWidth="true"/>
     <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="4" max="4" width="11.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
     <col min="5" max="5" width="11.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2379,7 +2577,7 @@
         <v>1.5336895236345123</v>
       </c>
       <c r="D2" s="0">
-        <v>1.4440969626615074</v>
+        <v>1.4675826035160828</v>
       </c>
       <c r="E2" s="0">
         <v>1.1438307958041567</v>
@@ -2396,7 +2594,7 @@
         <v>1.0996958454837389</v>
       </c>
       <c r="D3" s="0">
-        <v>1.3387601597193344</v>
+        <v>0.78707328071411398</v>
       </c>
       <c r="E3" s="0">
         <v>2.0007844145255982</v>
@@ -2413,7 +2611,7 @@
         <v>1.4651793487860167</v>
       </c>
       <c r="D4" s="0">
-        <v>1.7986121491619631</v>
+        <v>0.98022368407427884</v>
       </c>
       <c r="E4" s="0">
         <v>2.5487933810041188</v>
@@ -2430,7 +2628,7 @@
         <v>1.6145440396135229</v>
       </c>
       <c r="D5" s="0">
-        <v>1.9275693004963792</v>
+        <v>0.73127142985848537</v>
       </c>
       <c r="E5" s="0">
         <v>2.6333853691182521</v>
@@ -2447,7 +2645,7 @@
         <v>2.0373444465812938</v>
       </c>
       <c r="D6" s="0">
-        <v>2.0596311866574153</v>
+        <v>0.98019605881960659</v>
       </c>
       <c r="E6" s="0">
         <v>3.0563453096889193</v>
@@ -2464,7 +2662,7 @@
         <v>2.4862695491450117</v>
       </c>
       <c r="D7" s="0">
-        <v>2.5918754868357357</v>
+        <v>1.3455555465822089</v>
       </c>
       <c r="E7" s="0">
         <v>4.1486853301192559</v>
@@ -2481,7 +2679,7 @@
         <v>2.2473902473902472</v>
       </c>
       <c r="D8" s="0">
-        <v>2.8511368511368502</v>
+        <v>1.56027456027456</v>
       </c>
       <c r="E8" s="0">
         <v>4.2112098430731804</v>
@@ -2498,7 +2696,7 @@
         <v>2.5027180587844589</v>
       </c>
       <c r="D9" s="0">
-        <v>2.7151066713241865</v>
+        <v>1.6709349006952003</v>
       </c>
       <c r="E9" s="0">
         <v>4.0567375169517215</v>
@@ -2515,7 +2713,7 @@
         <v>2.0378755618980122</v>
       </c>
       <c r="D10" s="0">
-        <v>2.3244951598062875</v>
+        <v>1.418642900293837</v>
       </c>
       <c r="E10" s="0">
         <v>3.9537559662040795</v>
@@ -2532,7 +2730,7 @@
         <v>1.744535917580917</v>
       </c>
       <c r="D11" s="0">
-        <v>1.8264579275673956</v>
+        <v>1.7525938202025382</v>
       </c>
       <c r="E11" s="0">
         <v>3.1438931878746499</v>
@@ -2549,7 +2747,7 @@
         <v>1.6738206443413512</v>
       </c>
       <c r="D12" s="0">
-        <v>1.4480494876627501</v>
+        <v>1.8968440790319758</v>
       </c>
       <c r="E12" s="0">
         <v>2.8237515995029057</v>
@@ -2566,7 +2764,7 @@
         <v>1.2281292025994892</v>
       </c>
       <c r="D13" s="0">
-        <v>1.1949872230996048</v>
+        <v>1.7765351652673878</v>
       </c>
       <c r="E13" s="0">
         <v>2.6575886279450525</v>
@@ -2583,7 +2781,7 @@
         <v>1.3257457058277033</v>
       </c>
       <c r="D14" s="0">
-        <v>1.44259598022601</v>
+        <v>1.7474645973804379</v>
       </c>
       <c r="E14" s="0">
         <v>3.4340332928975501</v>
@@ -2607,16 +2805,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2633,7 +2831,7 @@
         <v>0.79575825825825841</v>
       </c>
       <c r="D2" s="0">
-        <v>0.50505721479054821</v>
+        <v>0.49927192040525381</v>
       </c>
       <c r="E2" s="0">
         <v>0.36063063063063067</v>
@@ -2650,7 +2848,7 @@
         <v>0.38835485485485494</v>
       </c>
       <c r="D3" s="0">
-        <v>0.45714664664664667</v>
+        <v>0.10870070070070073</v>
       </c>
       <c r="E3" s="0">
         <v>1.5484009009009014</v>
@@ -2667,7 +2865,7 @@
         <v>0.67179548731121053</v>
       </c>
       <c r="D4" s="0">
-        <v>0.88759362507161221</v>
+        <v>0.11234326150049424</v>
       </c>
       <c r="E4" s="0">
         <v>2.4934459459459464</v>
@@ -2684,7 +2882,7 @@
         <v>1.0831128949462281</v>
       </c>
       <c r="D5" s="0">
-        <v>1.1927328033161371</v>
+        <v>0.10523571006904341</v>
       </c>
       <c r="E5" s="0">
         <v>3.2241271271271255</v>
@@ -2701,7 +2899,7 @@
         <v>1.9614326679620799</v>
       </c>
       <c r="D6" s="0">
-        <v>1.5105909438850613</v>
+        <v>0.15847200141317788</v>
       </c>
       <c r="E6" s="0">
         <v>4.6041391391391393</v>
@@ -2718,7 +2916,7 @@
         <v>2.3403721855188508</v>
       </c>
       <c r="D7" s="0">
-        <v>2.0604970503837174</v>
+        <v>0.34601138471805132</v>
       </c>
       <c r="E7" s="0">
         <v>7.1557107107107125</v>
@@ -2735,7 +2933,7 @@
         <v>1.911840262030738</v>
       </c>
       <c r="D8" s="0">
-        <v>2.2283001709192178</v>
+        <v>0.37911363744697074</v>
       </c>
       <c r="E8" s="0">
         <v>6.985716716716718</v>
@@ -2752,7 +2950,7 @@
         <v>1.844060497997998</v>
       </c>
       <c r="D9" s="0">
-        <v>2.0533987737737744</v>
+        <v>0.48210535535535548</v>
       </c>
       <c r="E9" s="0">
         <v>6.0321136136136158</v>
@@ -2769,7 +2967,7 @@
         <v>1.4191883301741461</v>
       </c>
       <c r="D10" s="0">
-        <v>1.6329147374324682</v>
+        <v>0.52809325637694404</v>
       </c>
       <c r="E10" s="0">
         <v>6.1242572572572591</v>
@@ -2786,7 +2984,7 @@
         <v>0.94586106106106127</v>
       </c>
       <c r="D11" s="0">
-        <v>1.0645101101101095</v>
+        <v>0.75079739739739748</v>
       </c>
       <c r="E11" s="0">
         <v>4.5169491881818908</v>
@@ -2803,7 +3001,7 @@
         <v>0.78555605993590483</v>
       </c>
       <c r="D12" s="0">
-        <v>0.61183796975269855</v>
+        <v>1.0794662026367454</v>
       </c>
       <c r="E12" s="0">
         <v>3.8483844742178079</v>
@@ -2820,7 +3018,7 @@
         <v>0.54708334350610788</v>
       </c>
       <c r="D13" s="0">
-        <v>0.41481329296776448</v>
+        <v>1.2167355322802473</v>
       </c>
       <c r="E13" s="0">
         <v>3.6640834952599661</v>
@@ -2837,7 +3035,7 @@
         <v>0.52295456995456979</v>
       </c>
       <c r="D14" s="0">
-        <v>0.38408701008701007</v>
+        <v>1.1030324940324943</v>
       </c>
       <c r="E14" s="0">
         <v>4.8779485618952272</v>
@@ -2861,16 +3059,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -2885,7 +3083,7 @@
       </c>
       <c r="C2" s="0"/>
       <c r="D2" s="0">
-        <v>11.410604684127918</v>
+        <v>10.746956888314287</v>
       </c>
       <c r="E2" s="0"/>
     </row>
@@ -2898,7 +3096,7 @@
       </c>
       <c r="C3" s="0"/>
       <c r="D3" s="0">
-        <v>37.370084988860611</v>
+        <v>31.926983769247272</v>
       </c>
       <c r="E3" s="0"/>
     </row>
@@ -2911,7 +3109,7 @@
       </c>
       <c r="C4" s="0"/>
       <c r="D4" s="0">
-        <v>60.549607202022173</v>
+        <v>53.423469206462869</v>
       </c>
       <c r="E4" s="0"/>
     </row>
@@ -2924,7 +3122,7 @@
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0">
-        <v>75.123852494354139</v>
+        <v>66.850196024913373</v>
       </c>
       <c r="E5" s="0"/>
     </row>
@@ -2937,7 +3135,7 @@
       </c>
       <c r="C6" s="0"/>
       <c r="D6" s="0">
-        <v>82.711286382383662</v>
+        <v>74.532940054928844</v>
       </c>
       <c r="E6" s="0"/>
     </row>
@@ -2950,7 +3148,7 @@
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0">
-        <v>85.586291430282813</v>
+        <v>76.801480936934837</v>
       </c>
       <c r="E7" s="0"/>
     </row>
@@ -2963,7 +3161,7 @@
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0">
-        <v>67.160086894315981</v>
+        <v>56.865349564419517</v>
       </c>
       <c r="E8" s="0"/>
     </row>
@@ -2976,7 +3174,7 @@
       </c>
       <c r="C9" s="0"/>
       <c r="D9" s="0">
-        <v>46.184980846523018</v>
+        <v>35.358338665233973</v>
       </c>
       <c r="E9" s="0"/>
     </row>
@@ -2989,7 +3187,7 @@
       </c>
       <c r="C10" s="0"/>
       <c r="D10" s="0">
-        <v>42.421240880875956</v>
+        <v>30.851117708637446</v>
       </c>
       <c r="E10" s="0"/>
     </row>
@@ -3002,7 +3200,7 @@
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0">
-        <v>42.926118097596671</v>
+        <v>38.90790311515029</v>
       </c>
       <c r="E11" s="0"/>
     </row>
@@ -3015,7 +3213,7 @@
       </c>
       <c r="C12" s="0"/>
       <c r="D12" s="0">
-        <v>50.814808030159334</v>
+        <v>48.214967871429096</v>
       </c>
       <c r="E12" s="0"/>
     </row>
@@ -3028,7 +3226,7 @@
       </c>
       <c r="C13" s="0"/>
       <c r="D13" s="0">
-        <v>73.483807705387193</v>
+        <v>76.179223584738793</v>
       </c>
       <c r="E13" s="0"/>
     </row>
@@ -3041,7 +3239,7 @@
       </c>
       <c r="C14" s="0"/>
       <c r="D14" s="0">
-        <v>63.41597791157303</v>
+        <v>67.707593232564435</v>
       </c>
       <c r="E14" s="0"/>
     </row>
@@ -3063,16 +3261,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3087,7 +3285,7 @@
       </c>
       <c r="C2" s="0"/>
       <c r="D2" s="0">
-        <v>6.1031033074175696</v>
+        <v>6.2980661980671186</v>
       </c>
       <c r="E2" s="0"/>
     </row>
@@ -3100,7 +3298,7 @@
       </c>
       <c r="C3" s="0"/>
       <c r="D3" s="0">
-        <v>25.224455369473958</v>
+        <v>24.8091184013266</v>
       </c>
       <c r="E3" s="0"/>
     </row>
@@ -3113,7 +3311,7 @@
       </c>
       <c r="C4" s="0"/>
       <c r="D4" s="0">
-        <v>52.430884494124143</v>
+        <v>52.891107281147555</v>
       </c>
       <c r="E4" s="0"/>
     </row>
@@ -3126,7 +3324,7 @@
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0">
-        <v>77.546385236796198</v>
+        <v>75.535672407987107</v>
       </c>
       <c r="E5" s="0"/>
     </row>
@@ -3139,7 +3337,7 @@
       </c>
       <c r="C6" s="0"/>
       <c r="D6" s="0">
-        <v>99.183696300707595</v>
+        <v>95.061417187438167</v>
       </c>
       <c r="E6" s="0"/>
     </row>
@@ -3152,7 +3350,7 @@
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0">
-        <v>140.58760642256556</v>
+        <v>136.58475749508003</v>
       </c>
       <c r="E7" s="0"/>
     </row>
@@ -3165,7 +3363,7 @@
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0">
-        <v>153.65472171422394</v>
+        <v>145.26354252364533</v>
       </c>
       <c r="E8" s="0"/>
     </row>
@@ -3178,7 +3376,7 @@
       </c>
       <c r="C9" s="0"/>
       <c r="D9" s="0">
-        <v>119.73137405098797</v>
+        <v>117.46610374748606</v>
       </c>
       <c r="E9" s="0"/>
     </row>
@@ -3191,7 +3389,7 @@
       </c>
       <c r="C10" s="0"/>
       <c r="D10" s="0">
-        <v>90.981566486332298</v>
+        <v>89.984777084976201</v>
       </c>
       <c r="E10" s="0"/>
     </row>
@@ -3204,7 +3402,7 @@
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0">
-        <v>64.65483517296525</v>
+        <v>64.269397588158597</v>
       </c>
       <c r="E11" s="0"/>
     </row>
@@ -3217,7 +3415,7 @@
       </c>
       <c r="C12" s="0"/>
       <c r="D12" s="0">
-        <v>65.80135888438528</v>
+        <v>54.638505398683051</v>
       </c>
       <c r="E12" s="0"/>
     </row>
@@ -3230,7 +3428,7 @@
       </c>
       <c r="C13" s="0"/>
       <c r="D13" s="0">
-        <v>134.65738354268336</v>
+        <v>144.03080300000533</v>
       </c>
       <c r="E13" s="0"/>
     </row>
@@ -3243,7 +3441,7 @@
       </c>
       <c r="C14" s="0"/>
       <c r="D14" s="0">
-        <v>112.63311121604835</v>
+        <v>151.314966414271</v>
       </c>
       <c r="E14" s="0"/>
     </row>
@@ -3265,16 +3463,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3289,7 +3487,7 @@
       </c>
       <c r="C2" s="0"/>
       <c r="D2" s="0">
-        <v>0.0097006865624662177</v>
+        <v>0.013175905285370271</v>
       </c>
       <c r="E2" s="0"/>
     </row>
@@ -3302,7 +3500,7 @@
       </c>
       <c r="C3" s="0"/>
       <c r="D3" s="0">
-        <v>3.8421871719685951e-08</v>
+        <v>5.4222199839313927e-07</v>
       </c>
       <c r="E3" s="0"/>
     </row>
@@ -3315,7 +3513,7 @@
       </c>
       <c r="C4" s="0"/>
       <c r="D4" s="0">
-        <v>4.485577201150436e-13</v>
+        <v>1.4892225284090346e-11</v>
       </c>
       <c r="E4" s="0"/>
     </row>
@@ -3328,7 +3526,7 @@
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0">
-        <v>3.4084858466961797e-16</v>
+        <v>2.0161017616588476e-14</v>
       </c>
       <c r="E5" s="0"/>
     </row>
@@ -3341,7 +3539,7 @@
       </c>
       <c r="C6" s="0"/>
       <c r="D6" s="0">
-        <v>8.0418038451435731e-18</v>
+        <v>4.5625306611798857e-16</v>
       </c>
       <c r="E6" s="0"/>
     </row>
@@ -3354,7 +3552,7 @@
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0">
-        <v>1.9422421898629016e-18</v>
+        <v>1.4891670673398467e-16</v>
       </c>
       <c r="E7" s="0"/>
     </row>
@@ -3367,7 +3565,7 @@
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0">
-        <v>1.7305974918729271e-14</v>
+        <v>2.7457148787249849e-12</v>
       </c>
       <c r="E8" s="0"/>
     </row>
@@ -3380,7 +3578,7 @@
       </c>
       <c r="C9" s="0"/>
       <c r="D9" s="0">
-        <v>5.1804166535037941e-10</v>
+        <v>1.0233396476415416e-07</v>
       </c>
       <c r="E9" s="0"/>
     </row>
@@ -3393,7 +3591,7 @@
       </c>
       <c r="C10" s="0"/>
       <c r="D10" s="0">
-        <v>3.2656853580886856e-09</v>
+        <v>9.136698425394088e-07</v>
       </c>
       <c r="E10" s="0"/>
     </row>
@@ -3406,7 +3604,7 @@
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0">
-        <v>2.5515146534981529e-09</v>
+        <v>1.8154139683718205e-08</v>
       </c>
       <c r="E11" s="0"/>
     </row>
@@ -3419,7 +3617,7 @@
       </c>
       <c r="C12" s="0"/>
       <c r="D12" s="0">
-        <v>5.3573172621621168e-11</v>
+        <v>1.9165774576619879e-10</v>
       </c>
       <c r="E12" s="0"/>
     </row>
@@ -3432,7 +3630,7 @@
       </c>
       <c r="C13" s="0"/>
       <c r="D13" s="0">
-        <v>7.6563837316894364e-16</v>
+        <v>2.0246168078350906e-16</v>
       </c>
       <c r="E13" s="0"/>
     </row>
@@ -3445,7 +3643,7 @@
       </c>
       <c r="C14" s="0"/>
       <c r="D14" s="0">
-        <v>1.0942789073034149e-13</v>
+        <v>1.3213550866918925e-14</v>
       </c>
       <c r="E14" s="0"/>
     </row>
@@ -3467,16 +3665,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3491,7 +3689,7 @@
       </c>
       <c r="C2" s="0"/>
       <c r="D2" s="0">
-        <v>0.013494470094551554</v>
+        <v>0.012086975788492424</v>
       </c>
       <c r="E2" s="0"/>
     </row>
@@ -3504,7 +3702,7 @@
       </c>
       <c r="C3" s="0"/>
       <c r="D3" s="0">
-        <v>5.1030995221069119e-07</v>
+        <v>6.3297330811478278e-07</v>
       </c>
       <c r="E3" s="0"/>
     </row>
@@ -3517,7 +3715,7 @@
       </c>
       <c r="C4" s="0"/>
       <c r="D4" s="0">
-        <v>4.4565984665268264e-13</v>
+        <v>3.5256216948104571e-13</v>
       </c>
       <c r="E4" s="0"/>
     </row>
@@ -3530,7 +3728,7 @@
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0">
-        <v>1.2964185871991937e-18</v>
+        <v>3.5886453558667183e-18</v>
       </c>
       <c r="E5" s="0"/>
     </row>
@@ -3543,7 +3741,7 @@
       </c>
       <c r="C6" s="0"/>
       <c r="D6" s="0">
-        <v>2.3013383298971414e-23</v>
+        <v>1.8456919995877228e-22</v>
       </c>
       <c r="E6" s="0"/>
     </row>
@@ -3556,7 +3754,7 @@
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0">
-        <v>1.9802483301511833e-32</v>
+        <v>1.4863196789861074e-31</v>
       </c>
       <c r="E7" s="0"/>
     </row>
@@ -3569,7 +3767,7 @@
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0">
-        <v>2.7554108926037584e-35</v>
+        <v>1.8808075619485983e-33</v>
       </c>
       <c r="E8" s="0"/>
     </row>
@@ -3582,7 +3780,7 @@
       </c>
       <c r="C9" s="0"/>
       <c r="D9" s="0">
-        <v>7.2434271564687894e-28</v>
+        <v>2.2694562980612245e-27</v>
       </c>
       <c r="E9" s="0"/>
     </row>
@@ -3595,7 +3793,7 @@
       </c>
       <c r="C10" s="0"/>
       <c r="D10" s="0">
-        <v>1.4501680882865048e-21</v>
+        <v>2.3999954778645826e-21</v>
       </c>
       <c r="E10" s="0"/>
     </row>
@@ -3608,7 +3806,7 @@
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0">
-        <v>8.9237048816151297e-16</v>
+        <v>1.0851826065378379e-15</v>
       </c>
       <c r="E11" s="0"/>
     </row>
@@ -3621,7 +3819,7 @@
       </c>
       <c r="C12" s="0"/>
       <c r="D12" s="0">
-        <v>4.9873835648143897e-16</v>
+        <v>1.4486917793812948e-13</v>
       </c>
       <c r="E12" s="0"/>
     </row>
@@ -3634,7 +3832,7 @@
       </c>
       <c r="C13" s="0"/>
       <c r="D13" s="0">
-        <v>3.9235417411813785e-31</v>
+        <v>3.4982933680931276e-33</v>
       </c>
       <c r="E13" s="0"/>
     </row>
@@ -3647,7 +3845,7 @@
       </c>
       <c r="C14" s="0"/>
       <c r="D14" s="0">
-        <v>2.5963539838610194e-26</v>
+        <v>8.9443225878367405e-35</v>
       </c>
       <c r="E14" s="0"/>
     </row>
@@ -3669,16 +3867,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>4</v>
@@ -3695,7 +3893,7 @@
         <v>9.974381445021212</v>
       </c>
       <c r="D2" s="0">
-        <v>5.8185486540013702</v>
+        <v>6.2564441246887696</v>
       </c>
       <c r="E2" s="0">
         <v>2.2586231601201741</v>
@@ -3712,7 +3910,7 @@
         <v>4.4385055888523066</v>
       </c>
       <c r="D3" s="0">
-        <v>7.7449740536156311</v>
+        <v>4.7876632015097966</v>
       </c>
       <c r="E3" s="0">
         <v>5.6669440562861251</v>
@@ -3729,7 +3927,7 @@
         <v>7.1508145507835081</v>
       </c>
       <c r="D4" s="0">
-        <v>8.7905577328913882</v>
+        <v>5.1121989556372291</v>
       </c>
       <c r="E4" s="0">
         <v>4.9913330483747647</v>
@@ -3746,7 +3944,7 @@
         <v>8.0349533194253873</v>
       </c>
       <c r="D5" s="0">
-        <v>6.8471783334848215</v>
+        <v>4.8635225185416084</v>
       </c>
       <c r="E5" s="0">
         <v>8.9306938635495463</v>
@@ -3763,7 +3961,7 @@
         <v>6.6306018079982678</v>
       </c>
       <c r="D6" s="0">
-        <v>6.3598547741453011</v>
+        <v>4.7525023013450038</v>
       </c>
       <c r="E6" s="0">
         <v>8.6425707604296793</v>
@@ -3780,7 +3978,7 @@
         <v>6.6359314644677152</v>
       </c>
       <c r="D7" s="0">
-        <v>5.411967904524567</v>
+        <v>4.6909661526226873</v>
       </c>
       <c r="E7" s="0">
         <v>13.370425538638409</v>
@@ -3797,7 +3995,7 @@
         <v>7.5513340545422425</v>
       </c>
       <c r="D8" s="0">
-        <v>4.30418038698435</v>
+        <v>3.5981870312828961</v>
       </c>
       <c r="E8" s="0">
         <v>15.308569135295734</v>
@@ -3814,7 +4012,7 @@
         <v>6.4057179467690482</v>
       </c>
       <c r="D9" s="0">
-        <v>3.8952432055775441</v>
+        <v>3.6764198802672658</v>
       </c>
       <c r="E9" s="0">
         <v>15.403077006867361</v>
@@ -3831,7 +4029,7 @@
         <v>4.9139121523609317</v>
       </c>
       <c r="D10" s="0">
-        <v>3.2912492534791205</v>
+        <v>3.3229000086124634</v>
       </c>
       <c r="E10" s="0">
         <v>12.56871204259436</v>
@@ -3848,7 +4046,7 @@
         <v>3.1932905514201151</v>
       </c>
       <c r="D11" s="0">
-        <v>3.9856300418531525</v>
+        <v>3.3412602006674734</v>
       </c>
       <c r="E11" s="0">
         <v>10.265251123660747</v>
@@ -3865,7 +4063,7 @@
         <v>3.6656995525416329</v>
       </c>
       <c r="D12" s="0">
-        <v>5.4656044118402711</v>
+        <v>6.3255202286667505</v>
       </c>
       <c r="E12" s="0">
         <v>10.034027813502727</v>
@@ -3882,7 +4080,7 @@
         <v>3.168181664250092</v>
       </c>
       <c r="D13" s="0">
-        <v>6.351802400068089</v>
+        <v>4.1132954303778044</v>
       </c>
       <c r="E13" s="0">
         <v>12.330090161270089</v>
@@ -3899,7 +4097,7 @@
         <v>3.7161563688265318</v>
       </c>
       <c r="D14" s="0">
-        <v>5.566329221892925</v>
+        <v>4.1963859811454984</v>
       </c>
       <c r="E14" s="0">
         <v>11.314303718961998</v>
